--- a/new-model/matlab/result2.xlsx
+++ b/new-model/matlab/result2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="12">
   <si>
     <t>无人机编号</t>
   </si>
@@ -98,14 +98,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="true"/>
-    <col min="2" max="2" width="11.5546875" customWidth="true"/>
-    <col min="3" max="3" width="11.5546875" customWidth="true"/>
-    <col min="4" max="4" width="11.5546875" customWidth="true"/>
-    <col min="5" max="5" width="10.5546875" customWidth="true"/>
+    <col min="2" max="2" width="6.77734375" customWidth="true"/>
+    <col min="3" max="3" width="9.21875" customWidth="true"/>
+    <col min="4" max="4" width="10.5546875" customWidth="true"/>
+    <col min="5" max="5" width="11.5546875" customWidth="true"/>
     <col min="6" max="6" width="7.77734375" customWidth="true"/>
     <col min="7" max="7" width="11.5546875" customWidth="true"/>
     <col min="8" max="8" width="11.5546875" customWidth="true"/>
-    <col min="9" max="9" width="7.77734375" customWidth="true"/>
+    <col min="9" max="9" width="8.5546875" customWidth="true"/>
     <col min="10" max="10" width="11.5546875" customWidth="true"/>
     <col min="11" max="11" width="11.5546875" customWidth="true"/>
     <col min="12" max="12" width="13" customWidth="true"/>
@@ -154,37 +154,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="C2" s="0">
-        <v>100.5</v>
+        <v>80</v>
       </c>
       <c r="D2" s="0">
-        <v>17800</v>
+        <v>17927.688198433258</v>
       </c>
       <c r="E2" s="0">
-        <v>0</v>
+        <v>8.9288286392480387</v>
       </c>
       <c r="F2" s="0">
         <v>1800</v>
       </c>
       <c r="G2" s="0">
-        <v>17498.913195271496</v>
+        <v>17927.688198433258</v>
       </c>
       <c r="H2" s="0">
-        <v>15.779290807247557</v>
+        <v>8.9288286392480387</v>
       </c>
       <c r="I2" s="0">
-        <v>1755.9000000000001</v>
+        <v>1800</v>
       </c>
       <c r="J2" s="0">
-        <v>3</v>
+        <v>1.7780334472656247</v>
       </c>
       <c r="K2" s="0">
-        <v>6.2778991699218754</v>
+        <v>6.3539550781250007</v>
       </c>
       <c r="L2" s="0">
-        <v>3.2778991699218754</v>
+        <v>4.5759216308593764</v>
       </c>
     </row>
     <row r="3">
@@ -192,37 +192,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>325.00698037132401</v>
+        <v>304</v>
       </c>
       <c r="C3" s="0">
-        <v>130.45523830055129</v>
+        <v>117.5</v>
       </c>
       <c r="D3" s="0">
-        <v>13983.654916017722</v>
+        <v>12630.769595115002</v>
       </c>
       <c r="E3" s="0">
-        <v>11.390001804719759</v>
+        <v>464.84561815791301</v>
       </c>
       <c r="F3" s="0">
         <v>1400</v>
       </c>
       <c r="G3" s="0">
-        <v>13983.654916017722</v>
+        <v>12926.442842825159</v>
       </c>
       <c r="H3" s="0">
-        <v>11.390001804719759</v>
+        <v>26.492001669434728</v>
       </c>
       <c r="I3" s="0">
-        <v>1400</v>
+        <v>1300.7750000000001</v>
       </c>
       <c r="J3" s="0">
-        <v>18.561071240830373</v>
+        <v>14.944421386718751</v>
       </c>
       <c r="K3" s="0">
-        <v>19.763463818955373</v>
+        <v>18.848547363281252</v>
       </c>
       <c r="L3" s="0">
-        <v>1.202392578125</v>
+        <v>3.9041259765625007</v>
       </c>
     </row>
     <row r="4">
@@ -230,37 +230,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>71.56781671856767</v>
+        <v>74</v>
       </c>
       <c r="C4" s="0">
-        <v>72.61140725458516</v>
+        <v>117.5</v>
       </c>
       <c r="D4" s="0">
-        <v>6998.523556227703</v>
+        <v>6880.9369891911292</v>
       </c>
       <c r="E4" s="0">
-        <v>-3.9472961172150463</v>
+        <v>72.192380218867129</v>
       </c>
       <c r="F4" s="0">
         <v>700</v>
       </c>
       <c r="G4" s="0">
-        <v>6998.523556227703</v>
+        <v>6880.9369891911292</v>
       </c>
       <c r="H4" s="0">
-        <v>-3.9472961172150463</v>
+        <v>72.192380218867129</v>
       </c>
       <c r="I4" s="0">
         <v>700</v>
       </c>
       <c r="J4" s="0">
-        <v>43.492698418031758</v>
+        <v>29.288342285156247</v>
       </c>
       <c r="K4" s="0">
-        <v>43.585069023500509</v>
+        <v>32.301037597656247</v>
       </c>
       <c r="L4" s="0">
-        <v>0.092370605468751421</v>
+        <v>3.0126953125</v>
       </c>
     </row>
   </sheetData>
